--- a/Simulation/Results/p.mid_Ten.Fixed.Ints_mean.surv.10.xlsx
+++ b/Simulation/Results/p.mid_Ten.Fixed.Ints_mean.surv.10.xlsx
@@ -47,16 +47,16 @@
     <t xml:space="preserve">mid</t>
   </si>
   <si>
-    <t xml:space="preserve">4 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8 mins</t>
+    <t xml:space="preserve">5.1 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1 mins</t>
   </si>
 </sst>
 </file>
@@ -419,13 +419,13 @@
         <v>50</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0325</v>
+        <v>0.0273</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0262</v>
+        <v>0.0209</v>
       </c>
       <c r="D2" t="n">
-        <v>0.056</v>
+        <v>0.0483</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
@@ -448,13 +448,13 @@
         <v>100</v>
       </c>
       <c r="B3" t="n">
-        <v>0.039</v>
+        <v>0.0353</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0355</v>
+        <v>0.0301</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0705</v>
+        <v>0.0633</v>
       </c>
       <c r="E3" t="n">
         <v>0.1</v>
@@ -477,13 +477,13 @@
         <v>200</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0436</v>
+        <v>0.0402</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0415</v>
+        <v>0.0364</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0751</v>
+        <v>0.0663</v>
       </c>
       <c r="E4" t="n">
         <v>0.1</v>
@@ -506,13 +506,13 @@
         <v>500</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0491</v>
+        <v>0.0476</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0476</v>
+        <v>0.0465</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0828</v>
+        <v>0.0805</v>
       </c>
       <c r="E5" t="n">
         <v>0.1</v>
